--- a/product-definitions/spreadsheet/brightness-temperature.xlsx
+++ b/product-definitions/spreadsheet/brightness-temperature.xlsx
@@ -299,7 +299,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -325,11 +325,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -350,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -401,28 +396,25 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1872,7 +1864,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="8" t="s">
         <v>20</v>
       </c>
@@ -1880,7 +1872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="8" t="s">
         <v>27</v>
       </c>
@@ -1888,7 +1880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="8" t="s">
         <v>21</v>
       </c>
@@ -1896,10 +1888,10 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="C24" s="10"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>29</v>
       </c>
@@ -1907,7 +1899,7 @@
       <c r="C25" s="14"/>
       <c r="D25" s="13"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="13"/>
       <c r="B26" s="13" t="s">
         <v>11</v>
@@ -1917,7 +1909,7 @@
       </c>
       <c r="D26" s="13"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="13"/>
       <c r="B27" s="13" t="s">
         <v>13</v>
@@ -1927,7 +1919,7 @@
       </c>
       <c r="D27" s="13"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="13"/>
       <c r="B28" s="13" t="s">
         <v>2</v>
@@ -1937,7 +1929,7 @@
       </c>
       <c r="D28" s="13"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="13"/>
       <c r="B29" s="13" t="s">
         <v>14</v>
@@ -1947,7 +1939,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="13"/>
       <c r="B30" s="13" t="s">
         <v>15</v>
@@ -1957,7 +1949,7 @@
       </c>
       <c r="D30" s="13"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="13"/>
       <c r="B31" s="13" t="s">
         <v>17</v>
@@ -1967,7 +1959,7 @@
       </c>
       <c r="D31" s="13"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="13"/>
       <c r="B32" s="13" t="s">
         <v>18</v>
@@ -1977,7 +1969,7 @@
       </c>
       <c r="D32" s="13"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="13"/>
       <c r="B33" s="13" t="s">
         <v>20</v>
@@ -1987,7 +1979,7 @@
       </c>
       <c r="D33" s="13"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="13"/>
       <c r="B34" s="13" t="s">
         <v>27</v>
@@ -1997,7 +1989,7 @@
       </c>
       <c r="D34" s="13"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="13"/>
       <c r="B35" s="13" t="s">
         <v>21</v>
@@ -2007,10 +1999,10 @@
       </c>
       <c r="D35" s="13"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="C36" s="10"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="18" t="s">
         <v>32</v>
       </c>
@@ -2020,7 +2012,7 @@
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="18"/>
       <c r="B38" s="18" t="s">
         <v>11</v>
@@ -2032,7 +2024,7 @@
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="18"/>
       <c r="B39" s="18" t="s">
         <v>13</v>
@@ -2044,7 +2036,7 @@
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="18"/>
       <c r="B40" s="18" t="s">
         <v>2</v>
@@ -2056,7 +2048,7 @@
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="18"/>
       <c r="B41" s="18" t="s">
         <v>14</v>
@@ -2066,7 +2058,7 @@
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="18"/>
       <c r="B42" s="18" t="s">
         <v>15</v>
@@ -2078,7 +2070,7 @@
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="18"/>
       <c r="B43" s="18" t="s">
         <v>36</v>
@@ -2090,19 +2082,19 @@
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="18"/>
-      <c r="B44" s="22" t="s">
+      <c r="B44" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="22" t="s">
         <v>39</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="18"/>
       <c r="B45" s="18"/>
       <c r="C45" s="19"/>
@@ -2110,8 +2102,8 @@
       <c r="E45" s="18"/>
       <c r="F45" s="18"/>
     </row>
-    <row r="46">
-      <c r="A46" s="24" t="s">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="23" t="s">
         <v>40</v>
       </c>
       <c r="B46" s="18"/>
@@ -2120,7 +2112,7 @@
       <c r="E46" s="18"/>
       <c r="F46" s="18"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="18"/>
       <c r="B47" s="18" t="s">
         <v>11</v>
@@ -2132,7 +2124,7 @@
       <c r="E47" s="18"/>
       <c r="F47" s="18"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="18"/>
       <c r="B48" s="18" t="s">
         <v>13</v>
@@ -2144,7 +2136,7 @@
       <c r="E48" s="18"/>
       <c r="F48" s="18"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="18"/>
       <c r="B49" s="18" t="s">
         <v>2</v>
@@ -2156,7 +2148,7 @@
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="18"/>
       <c r="B50" s="18" t="s">
         <v>14</v>
@@ -2166,19 +2158,19 @@
       <c r="E50" s="18"/>
       <c r="F50" s="18"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="18"/>
       <c r="B51" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="24" t="s">
         <v>41</v>
       </c>
       <c r="D51" s="18"/>
       <c r="E51" s="18"/>
       <c r="F51" s="18"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="18"/>
       <c r="B52" s="18" t="s">
         <v>36</v>
@@ -2190,19 +2182,19 @@
       <c r="E52" s="18"/>
       <c r="F52" s="18"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="18"/>
-      <c r="B53" s="22" t="s">
+      <c r="B53" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>43</v>
       </c>
       <c r="D53" s="18"/>
       <c r="E53" s="18"/>
       <c r="F53" s="18"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
@@ -2210,7 +2202,7 @@
       <c r="E54" s="18"/>
       <c r="F54" s="18"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="18" t="s">
         <v>44</v>
       </c>
@@ -2220,7 +2212,7 @@
       <c r="E55" s="18"/>
       <c r="F55" s="18"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="18"/>
       <c r="B56" s="18" t="s">
         <v>45</v>
@@ -2232,7 +2224,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="18"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="18"/>
       <c r="B57" s="18" t="s">
         <v>11</v>
@@ -2244,7 +2236,7 @@
       <c r="E57" s="18"/>
       <c r="F57" s="18"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="18"/>
       <c r="B58" s="18" t="s">
         <v>13</v>
@@ -2256,7 +2248,7 @@
       <c r="E58" s="18"/>
       <c r="F58" s="18"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="18"/>
       <c r="B59" s="18" t="s">
         <v>2</v>
@@ -2268,7 +2260,7 @@
       <c r="E59" s="18"/>
       <c r="F59" s="18"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="18"/>
       <c r="B60" s="18" t="s">
         <v>14</v>
@@ -2278,7 +2270,7 @@
       <c r="E60" s="18"/>
       <c r="F60" s="18"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="18"/>
       <c r="B61" s="18" t="s">
         <v>15</v>
@@ -2290,7 +2282,7 @@
       <c r="E61" s="18"/>
       <c r="F61" s="18"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="18"/>
       <c r="B62" s="18" t="s">
         <v>36</v>
@@ -2302,19 +2294,19 @@
       <c r="E62" s="18"/>
       <c r="F62" s="18"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="18"/>
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>47</v>
       </c>
       <c r="D63" s="18"/>
       <c r="E63" s="18"/>
       <c r="F63" s="18"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="18"/>
       <c r="B64" s="18"/>
       <c r="C64" s="19"/>
@@ -2322,7 +2314,7 @@
       <c r="E64" s="18"/>
       <c r="F64" s="18"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="18" t="s">
         <v>48</v>
       </c>
@@ -2332,7 +2324,7 @@
       <c r="E65" s="18"/>
       <c r="F65" s="18"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="18"/>
       <c r="B66" s="18" t="s">
         <v>45</v>
@@ -2344,7 +2336,7 @@
       <c r="E66" s="18"/>
       <c r="F66" s="18"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="18"/>
       <c r="B67" s="18" t="s">
         <v>11</v>
@@ -2356,7 +2348,7 @@
       <c r="E67" s="18"/>
       <c r="F67" s="18"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="18"/>
       <c r="B68" s="18" t="s">
         <v>13</v>
@@ -2368,7 +2360,7 @@
       <c r="E68" s="18"/>
       <c r="F68" s="18"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="18"/>
       <c r="B69" s="18" t="s">
         <v>2</v>
@@ -2380,7 +2372,7 @@
       <c r="E69" s="18"/>
       <c r="F69" s="18"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="18"/>
       <c r="B70" s="18" t="s">
         <v>14</v>
@@ -2390,7 +2382,7 @@
       <c r="E70" s="18"/>
       <c r="F70" s="18"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="18"/>
       <c r="B71" s="18" t="s">
         <v>15</v>
@@ -2402,7 +2394,7 @@
       <c r="E71" s="18"/>
       <c r="F71" s="18"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="18"/>
       <c r="B72" s="18" t="s">
         <v>36</v>
@@ -2414,19 +2406,19 @@
       <c r="E72" s="18"/>
       <c r="F72" s="18"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="18"/>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="22" t="s">
         <v>50</v>
       </c>
       <c r="D73" s="18"/>
       <c r="E73" s="18"/>
       <c r="F73" s="18"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="18"/>
       <c r="B74" s="18"/>
       <c r="C74" s="20"/>
@@ -2434,8 +2426,8 @@
       <c r="E74" s="18"/>
       <c r="F74" s="18"/>
     </row>
-    <row r="75">
-      <c r="A75" s="24" t="s">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="23" t="s">
         <v>51</v>
       </c>
       <c r="B75" s="18"/>
@@ -2444,7 +2436,7 @@
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="18"/>
       <c r="B76" s="18" t="s">
         <v>45</v>
@@ -2456,7 +2448,7 @@
       <c r="E76" s="18"/>
       <c r="F76" s="18"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="18"/>
       <c r="B77" s="18" t="s">
         <v>11</v>
@@ -2468,7 +2460,7 @@
       <c r="E77" s="18"/>
       <c r="F77" s="18"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="18"/>
       <c r="B78" s="18" t="s">
         <v>13</v>
@@ -2480,7 +2472,7 @@
       <c r="E78" s="18"/>
       <c r="F78" s="18"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="18"/>
       <c r="B79" s="18" t="s">
         <v>2</v>
@@ -2492,7 +2484,7 @@
       <c r="E79" s="18"/>
       <c r="F79" s="18"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="18"/>
       <c r="B80" s="18" t="s">
         <v>14</v>
@@ -2502,19 +2494,19 @@
       <c r="E80" s="18"/>
       <c r="F80" s="18"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="18"/>
       <c r="B81" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="24" t="s">
         <v>52</v>
       </c>
       <c r="D81" s="18"/>
       <c r="E81" s="18"/>
       <c r="F81" s="18"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="18"/>
       <c r="B82" s="18" t="s">
         <v>36</v>
@@ -2526,19 +2518,19 @@
       <c r="E82" s="18"/>
       <c r="F82" s="18"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="18"/>
-      <c r="B83" s="22" t="s">
+      <c r="B83" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D83" s="18"/>
       <c r="E83" s="18"/>
       <c r="F83" s="18"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="18"/>
       <c r="B84" s="18"/>
       <c r="C84" s="19"/>
@@ -2546,8 +2538,8 @@
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
     </row>
-    <row r="85">
-      <c r="A85" s="24" t="s">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="23" t="s">
         <v>54</v>
       </c>
       <c r="B85" s="18"/>
@@ -2556,7 +2548,7 @@
       <c r="E85" s="18"/>
       <c r="F85" s="18"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="18"/>
       <c r="B86" s="18" t="s">
         <v>11</v>
@@ -2568,7 +2560,7 @@
       <c r="E86" s="18"/>
       <c r="F86" s="18"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="18"/>
       <c r="B87" s="18" t="s">
         <v>13</v>
@@ -2580,7 +2572,7 @@
       <c r="E87" s="18"/>
       <c r="F87" s="18"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="18"/>
       <c r="B88" s="18" t="s">
         <v>2</v>
@@ -2592,7 +2584,7 @@
       <c r="E88" s="18"/>
       <c r="F88" s="18"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="18"/>
       <c r="B89" s="18" t="s">
         <v>14</v>
@@ -2602,19 +2594,19 @@
       <c r="E89" s="18"/>
       <c r="F89" s="18"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="18"/>
       <c r="B90" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="25" t="s">
+      <c r="C90" s="24" t="s">
         <v>55</v>
       </c>
       <c r="D90" s="18"/>
       <c r="E90" s="18"/>
       <c r="F90" s="18"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="18"/>
       <c r="B91" s="18" t="s">
         <v>36</v>
@@ -2626,19 +2618,19 @@
       <c r="E91" s="18"/>
       <c r="F91" s="18"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="18"/>
-      <c r="B92" s="22" t="s">
+      <c r="B92" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D92" s="18"/>
       <c r="E92" s="18"/>
       <c r="F92" s="18"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="18"/>
       <c r="B93" s="18"/>
       <c r="C93" s="19"/>
@@ -2646,8 +2638,8 @@
       <c r="E93" s="18"/>
       <c r="F93" s="18"/>
     </row>
-    <row r="94">
-      <c r="A94" s="24" t="s">
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="23" t="s">
         <v>56</v>
       </c>
       <c r="B94" s="18"/>
@@ -2656,7 +2648,7 @@
       <c r="E94" s="18"/>
       <c r="F94" s="18"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="18"/>
       <c r="B95" s="18" t="s">
         <v>11</v>
@@ -2668,7 +2660,7 @@
       <c r="E95" s="18"/>
       <c r="F95" s="18"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="18"/>
       <c r="B96" s="18" t="s">
         <v>13</v>
@@ -2680,7 +2672,7 @@
       <c r="E96" s="18"/>
       <c r="F96" s="18"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="18"/>
       <c r="B97" s="18" t="s">
         <v>2</v>
@@ -2692,7 +2684,7 @@
       <c r="E97" s="18"/>
       <c r="F97" s="18"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="18"/>
       <c r="B98" s="18" t="s">
         <v>14</v>
@@ -2702,19 +2694,19 @@
       <c r="E98" s="18"/>
       <c r="F98" s="18"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="18"/>
       <c r="B99" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="25" t="s">
+      <c r="C99" s="24" t="s">
         <v>57</v>
       </c>
       <c r="D99" s="18"/>
       <c r="E99" s="18"/>
       <c r="F99" s="18"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="18"/>
       <c r="B100" s="18" t="s">
         <v>36</v>
@@ -2726,19 +2718,19 @@
       <c r="E100" s="18"/>
       <c r="F100" s="18"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="18"/>
-      <c r="B101" s="22" t="s">
+      <c r="B101" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D101" s="18"/>
       <c r="E101" s="18"/>
       <c r="F101" s="18"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="18"/>
       <c r="B102" s="18"/>
       <c r="C102" s="19"/>
@@ -2746,8 +2738,8 @@
       <c r="E102" s="18"/>
       <c r="F102" s="18"/>
     </row>
-    <row r="103">
-      <c r="A103" s="24" t="s">
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="23" t="s">
         <v>58</v>
       </c>
       <c r="B103" s="18"/>
@@ -2756,7 +2748,7 @@
       <c r="E103" s="18"/>
       <c r="F103" s="18"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="18"/>
       <c r="B104" s="18" t="s">
         <v>11</v>
@@ -2768,7 +2760,7 @@
       <c r="E104" s="18"/>
       <c r="F104" s="18"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="18"/>
       <c r="B105" s="18" t="s">
         <v>13</v>
@@ -2780,7 +2772,7 @@
       <c r="E105" s="18"/>
       <c r="F105" s="18"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="18"/>
       <c r="B106" s="18" t="s">
         <v>2</v>
@@ -2792,7 +2784,7 @@
       <c r="E106" s="18"/>
       <c r="F106" s="18"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="18"/>
       <c r="B107" s="18" t="s">
         <v>14</v>
@@ -2802,19 +2794,19 @@
       <c r="E107" s="18"/>
       <c r="F107" s="18"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="18"/>
       <c r="B108" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="25" t="s">
+      <c r="C108" s="24" t="s">
         <v>59</v>
       </c>
       <c r="D108" s="18"/>
       <c r="E108" s="18"/>
       <c r="F108" s="18"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="18"/>
       <c r="B109" s="18" t="s">
         <v>36</v>
@@ -2826,19 +2818,19 @@
       <c r="E109" s="18"/>
       <c r="F109" s="18"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="18"/>
-      <c r="B110" s="22" t="s">
+      <c r="B110" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C110" s="23" t="s">
+      <c r="C110" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D110" s="18"/>
       <c r="E110" s="18"/>
       <c r="F110" s="18"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="18"/>
       <c r="B111" s="18"/>
       <c r="C111" s="19"/>
@@ -2846,8 +2838,8 @@
       <c r="E111" s="18"/>
       <c r="F111" s="18"/>
     </row>
-    <row r="112">
-      <c r="A112" s="24" t="s">
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="23" t="s">
         <v>60</v>
       </c>
       <c r="B112" s="18"/>
@@ -2856,7 +2848,7 @@
       <c r="E112" s="18"/>
       <c r="F112" s="18"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="18"/>
       <c r="B113" s="18" t="s">
         <v>11</v>
@@ -2868,7 +2860,7 @@
       <c r="E113" s="18"/>
       <c r="F113" s="18"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="18"/>
       <c r="B114" s="18" t="s">
         <v>13</v>
@@ -2880,7 +2872,7 @@
       <c r="E114" s="18"/>
       <c r="F114" s="18"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="18"/>
       <c r="B115" s="18" t="s">
         <v>2</v>
@@ -2892,7 +2884,7 @@
       <c r="E115" s="18"/>
       <c r="F115" s="18"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="18"/>
       <c r="B116" s="18" t="s">
         <v>14</v>
@@ -2902,19 +2894,19 @@
       <c r="E116" s="18"/>
       <c r="F116" s="18"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="18"/>
       <c r="B117" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C117" s="25" t="s">
+      <c r="C117" s="24" t="s">
         <v>61</v>
       </c>
       <c r="D117" s="18"/>
       <c r="E117" s="18"/>
       <c r="F117" s="18"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="18"/>
       <c r="B118" s="18" t="s">
         <v>36</v>
@@ -2926,19 +2918,19 @@
       <c r="E118" s="18"/>
       <c r="F118" s="18"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="18"/>
-      <c r="B119" s="22" t="s">
+      <c r="B119" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C119" s="23" t="s">
+      <c r="C119" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D119" s="18"/>
       <c r="E119" s="18"/>
       <c r="F119" s="18"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="18"/>
       <c r="B120" s="18"/>
       <c r="C120" s="19"/>
@@ -2946,8 +2938,8 @@
       <c r="E120" s="18"/>
       <c r="F120" s="18"/>
     </row>
-    <row r="121">
-      <c r="A121" s="24" t="s">
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="23" t="s">
         <v>62</v>
       </c>
       <c r="B121" s="18"/>
@@ -2956,7 +2948,7 @@
       <c r="E121" s="18"/>
       <c r="F121" s="18"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="18"/>
       <c r="B122" s="18" t="s">
         <v>11</v>
@@ -2968,7 +2960,7 @@
       <c r="E122" s="18"/>
       <c r="F122" s="18"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="18"/>
       <c r="B123" s="18" t="s">
         <v>13</v>
@@ -2980,7 +2972,7 @@
       <c r="E123" s="18"/>
       <c r="F123" s="18"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="18"/>
       <c r="B124" s="18" t="s">
         <v>2</v>
@@ -2992,7 +2984,7 @@
       <c r="E124" s="18"/>
       <c r="F124" s="18"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="18"/>
       <c r="B125" s="18" t="s">
         <v>14</v>
@@ -3002,19 +2994,19 @@
       <c r="E125" s="18"/>
       <c r="F125" s="18"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="18"/>
       <c r="B126" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C126" s="25" t="s">
+      <c r="C126" s="24" t="s">
         <v>63</v>
       </c>
       <c r="D126" s="18"/>
       <c r="E126" s="18"/>
       <c r="F126" s="18"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="18"/>
       <c r="B127" s="18" t="s">
         <v>36</v>
@@ -3026,19 +3018,19 @@
       <c r="E127" s="18"/>
       <c r="F127" s="18"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="18"/>
-      <c r="B128" s="22" t="s">
+      <c r="B128" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C128" s="23" t="s">
+      <c r="C128" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D128" s="18"/>
       <c r="E128" s="18"/>
       <c r="F128" s="18"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="18"/>
       <c r="B129" s="18"/>
       <c r="C129" s="19"/>
@@ -3046,8 +3038,8 @@
       <c r="E129" s="18"/>
       <c r="F129" s="18"/>
     </row>
-    <row r="130">
-      <c r="A130" s="24" t="s">
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="23" t="s">
         <v>64</v>
       </c>
       <c r="B130" s="18"/>
@@ -3056,7 +3048,7 @@
       <c r="E130" s="18"/>
       <c r="F130" s="18"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="18"/>
       <c r="B131" s="18" t="s">
         <v>11</v>
@@ -3068,7 +3060,7 @@
       <c r="E131" s="18"/>
       <c r="F131" s="18"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="18"/>
       <c r="B132" s="18" t="s">
         <v>13</v>
@@ -3080,7 +3072,7 @@
       <c r="E132" s="18"/>
       <c r="F132" s="18"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="18"/>
       <c r="B133" s="18" t="s">
         <v>2</v>
@@ -3092,7 +3084,7 @@
       <c r="E133" s="18"/>
       <c r="F133" s="18"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="18"/>
       <c r="B134" s="18" t="s">
         <v>14</v>
@@ -3102,19 +3094,19 @@
       <c r="E134" s="18"/>
       <c r="F134" s="18"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="18"/>
       <c r="B135" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C135" s="25" t="s">
+      <c r="C135" s="24" t="s">
         <v>65</v>
       </c>
       <c r="D135" s="18"/>
       <c r="E135" s="18"/>
       <c r="F135" s="18"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="18"/>
       <c r="B136" s="18" t="s">
         <v>36</v>
@@ -3126,19 +3118,19 @@
       <c r="E136" s="18"/>
       <c r="F136" s="18"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="18"/>
-      <c r="B137" s="22" t="s">
+      <c r="B137" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C137" s="23" t="s">
+      <c r="C137" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D137" s="18"/>
       <c r="E137" s="18"/>
       <c r="F137" s="18"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="18"/>
       <c r="B138" s="18"/>
       <c r="C138" s="19"/>
@@ -3146,8 +3138,8 @@
       <c r="E138" s="18"/>
       <c r="F138" s="18"/>
     </row>
-    <row r="139">
-      <c r="A139" s="24" t="s">
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="23" t="s">
         <v>66</v>
       </c>
       <c r="B139" s="18"/>
@@ -3156,7 +3148,7 @@
       <c r="E139" s="18"/>
       <c r="F139" s="18"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="18"/>
       <c r="B140" s="18" t="s">
         <v>11</v>
@@ -3168,7 +3160,7 @@
       <c r="E140" s="18"/>
       <c r="F140" s="18"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="18"/>
       <c r="B141" s="18" t="s">
         <v>13</v>
@@ -3180,7 +3172,7 @@
       <c r="E141" s="18"/>
       <c r="F141" s="18"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="18"/>
       <c r="B142" s="18" t="s">
         <v>2</v>
@@ -3192,7 +3184,7 @@
       <c r="E142" s="18"/>
       <c r="F142" s="18"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="18"/>
       <c r="B143" s="18" t="s">
         <v>14</v>
@@ -3202,19 +3194,19 @@
       <c r="E143" s="18"/>
       <c r="F143" s="18"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="18"/>
       <c r="B144" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="25" t="s">
+      <c r="C144" s="24" t="s">
         <v>67</v>
       </c>
       <c r="D144" s="18"/>
       <c r="E144" s="18"/>
       <c r="F144" s="18"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="18"/>
       <c r="B145" s="18" t="s">
         <v>36</v>
@@ -3226,19 +3218,19 @@
       <c r="E145" s="18"/>
       <c r="F145" s="18"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="18"/>
-      <c r="B146" s="22" t="s">
+      <c r="B146" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C146" s="23" t="s">
+      <c r="C146" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D146" s="18"/>
       <c r="E146" s="18"/>
       <c r="F146" s="18"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="18"/>
       <c r="B147" s="18"/>
       <c r="C147" s="19"/>
@@ -3246,8 +3238,8 @@
       <c r="E147" s="18"/>
       <c r="F147" s="18"/>
     </row>
-    <row r="148">
-      <c r="A148" s="24" t="s">
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="23" t="s">
         <v>68</v>
       </c>
       <c r="B148" s="18"/>
@@ -3256,7 +3248,7 @@
       <c r="E148" s="18"/>
       <c r="F148" s="18"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="18"/>
       <c r="B149" s="18" t="s">
         <v>11</v>
@@ -3268,7 +3260,7 @@
       <c r="E149" s="18"/>
       <c r="F149" s="18"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="18"/>
       <c r="B150" s="18" t="s">
         <v>13</v>
@@ -3280,7 +3272,7 @@
       <c r="E150" s="18"/>
       <c r="F150" s="18"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="18"/>
       <c r="B151" s="18" t="s">
         <v>2</v>
@@ -3292,7 +3284,7 @@
       <c r="E151" s="18"/>
       <c r="F151" s="18"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="18"/>
       <c r="B152" s="18" t="s">
         <v>14</v>
@@ -3302,19 +3294,19 @@
       <c r="E152" s="18"/>
       <c r="F152" s="18"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="18"/>
       <c r="B153" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C153" s="25" t="s">
+      <c r="C153" s="24" t="s">
         <v>69</v>
       </c>
       <c r="D153" s="18"/>
       <c r="E153" s="18"/>
       <c r="F153" s="18"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="18"/>
       <c r="B154" s="18" t="s">
         <v>36</v>
@@ -3326,19 +3318,19 @@
       <c r="E154" s="18"/>
       <c r="F154" s="18"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="18"/>
-      <c r="B155" s="22" t="s">
+      <c r="B155" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C155" s="23" t="s">
+      <c r="C155" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D155" s="18"/>
       <c r="E155" s="18"/>
       <c r="F155" s="18"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="18"/>
       <c r="B156" s="18"/>
       <c r="C156" s="19"/>
@@ -3346,8 +3338,8 @@
       <c r="E156" s="18"/>
       <c r="F156" s="18"/>
     </row>
-    <row r="157">
-      <c r="A157" s="24" t="s">
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="23" t="s">
         <v>70</v>
       </c>
       <c r="B157" s="18"/>
@@ -3356,7 +3348,7 @@
       <c r="E157" s="18"/>
       <c r="F157" s="18"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="18"/>
       <c r="B158" s="18" t="s">
         <v>11</v>
@@ -3368,7 +3360,7 @@
       <c r="E158" s="18"/>
       <c r="F158" s="18"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="18"/>
       <c r="B159" s="18" t="s">
         <v>13</v>
@@ -3380,7 +3372,7 @@
       <c r="E159" s="18"/>
       <c r="F159" s="18"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="18"/>
       <c r="B160" s="18" t="s">
         <v>2</v>
@@ -3392,7 +3384,7 @@
       <c r="E160" s="18"/>
       <c r="F160" s="18"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="18"/>
       <c r="B161" s="18" t="s">
         <v>14</v>
@@ -3402,19 +3394,19 @@
       <c r="E161" s="18"/>
       <c r="F161" s="18"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="18"/>
       <c r="B162" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="25" t="s">
+      <c r="C162" s="24" t="s">
         <v>71</v>
       </c>
       <c r="D162" s="18"/>
       <c r="E162" s="18"/>
       <c r="F162" s="18"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="18"/>
       <c r="B163" s="18" t="s">
         <v>36</v>
@@ -3426,19 +3418,19 @@
       <c r="E163" s="18"/>
       <c r="F163" s="18"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="18"/>
-      <c r="B164" s="22" t="s">
+      <c r="B164" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C164" s="23" t="s">
+      <c r="C164" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D164" s="18"/>
       <c r="E164" s="18"/>
       <c r="F164" s="18"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="18"/>
       <c r="B165" s="18"/>
       <c r="C165" s="19"/>
@@ -3446,8 +3438,8 @@
       <c r="E165" s="18"/>
       <c r="F165" s="18"/>
     </row>
-    <row r="166">
-      <c r="A166" s="24" t="s">
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="23" t="s">
         <v>72</v>
       </c>
       <c r="B166" s="18"/>
@@ -3456,7 +3448,7 @@
       <c r="E166" s="18"/>
       <c r="F166" s="18"/>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="18"/>
       <c r="B167" s="18" t="s">
         <v>11</v>
@@ -3468,7 +3460,7 @@
       <c r="E167" s="18"/>
       <c r="F167" s="18"/>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="18"/>
       <c r="B168" s="18" t="s">
         <v>13</v>
@@ -3480,7 +3472,7 @@
       <c r="E168" s="18"/>
       <c r="F168" s="18"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="18"/>
       <c r="B169" s="18" t="s">
         <v>2</v>
@@ -3492,7 +3484,7 @@
       <c r="E169" s="18"/>
       <c r="F169" s="18"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="18"/>
       <c r="B170" s="18" t="s">
         <v>14</v>
@@ -3502,19 +3494,19 @@
       <c r="E170" s="18"/>
       <c r="F170" s="18"/>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="18"/>
       <c r="B171" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="25" t="s">
+      <c r="C171" s="24" t="s">
         <v>73</v>
       </c>
       <c r="D171" s="18"/>
       <c r="E171" s="18"/>
       <c r="F171" s="18"/>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="18"/>
       <c r="B172" s="18" t="s">
         <v>36</v>
@@ -3526,19 +3518,19 @@
       <c r="E172" s="18"/>
       <c r="F172" s="18"/>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="18"/>
-      <c r="B173" s="22" t="s">
+      <c r="B173" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C173" s="23" t="s">
+      <c r="C173" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D173" s="18"/>
       <c r="E173" s="18"/>
       <c r="F173" s="18"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="18"/>
       <c r="B174" s="18"/>
       <c r="C174" s="19"/>
@@ -3546,8 +3538,8 @@
       <c r="E174" s="18"/>
       <c r="F174" s="18"/>
     </row>
-    <row r="175">
-      <c r="A175" s="24" t="s">
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="23" t="s">
         <v>74</v>
       </c>
       <c r="B175" s="18"/>
@@ -3556,7 +3548,7 @@
       <c r="E175" s="18"/>
       <c r="F175" s="18"/>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="18"/>
       <c r="B176" s="18" t="s">
         <v>11</v>
@@ -3568,7 +3560,7 @@
       <c r="E176" s="18"/>
       <c r="F176" s="18"/>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="18"/>
       <c r="B177" s="18" t="s">
         <v>13</v>
@@ -3580,7 +3572,7 @@
       <c r="E177" s="18"/>
       <c r="F177" s="18"/>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="18"/>
       <c r="B178" s="18" t="s">
         <v>2</v>
@@ -3592,7 +3584,7 @@
       <c r="E178" s="18"/>
       <c r="F178" s="18"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="18"/>
       <c r="B179" s="18" t="s">
         <v>14</v>
@@ -3602,19 +3594,19 @@
       <c r="E179" s="18"/>
       <c r="F179" s="18"/>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="18"/>
       <c r="B180" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C180" s="25" t="s">
+      <c r="C180" s="24" t="s">
         <v>75</v>
       </c>
       <c r="D180" s="18"/>
       <c r="E180" s="18"/>
       <c r="F180" s="18"/>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="18"/>
       <c r="B181" s="18" t="s">
         <v>36</v>
@@ -3626,19 +3618,19 @@
       <c r="E181" s="18"/>
       <c r="F181" s="18"/>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="18"/>
-      <c r="B182" s="22" t="s">
+      <c r="B182" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C182" s="23" t="s">
+      <c r="C182" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D182" s="18"/>
       <c r="E182" s="18"/>
       <c r="F182" s="18"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="18"/>
       <c r="B183" s="18"/>
       <c r="C183" s="19"/>
@@ -3646,8 +3638,8 @@
       <c r="E183" s="18"/>
       <c r="F183" s="18"/>
     </row>
-    <row r="184">
-      <c r="A184" s="24" t="s">
+    <row r="184" ht="15.75" customHeight="1">
+      <c r="A184" s="23" t="s">
         <v>76</v>
       </c>
       <c r="B184" s="18"/>
@@ -3656,7 +3648,7 @@
       <c r="E184" s="18"/>
       <c r="F184" s="18"/>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="18"/>
       <c r="B185" s="18" t="s">
         <v>11</v>
@@ -3668,7 +3660,7 @@
       <c r="E185" s="18"/>
       <c r="F185" s="18"/>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="18"/>
       <c r="B186" s="18" t="s">
         <v>13</v>
@@ -3680,7 +3672,7 @@
       <c r="E186" s="18"/>
       <c r="F186" s="18"/>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="18"/>
       <c r="B187" s="18" t="s">
         <v>2</v>
@@ -3692,7 +3684,7 @@
       <c r="E187" s="18"/>
       <c r="F187" s="18"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="18"/>
       <c r="B188" s="18" t="s">
         <v>14</v>
@@ -3702,19 +3694,19 @@
       <c r="E188" s="18"/>
       <c r="F188" s="18"/>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="18"/>
       <c r="B189" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C189" s="25" t="s">
+      <c r="C189" s="24" t="s">
         <v>77</v>
       </c>
       <c r="D189" s="18"/>
       <c r="E189" s="18"/>
       <c r="F189" s="18"/>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="18"/>
       <c r="B190" s="18" t="s">
         <v>36</v>
@@ -3726,19 +3718,19 @@
       <c r="E190" s="18"/>
       <c r="F190" s="18"/>
     </row>
-    <row r="191">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="18"/>
-      <c r="B191" s="22" t="s">
+      <c r="B191" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C191" s="23" t="s">
+      <c r="C191" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D191" s="18"/>
       <c r="E191" s="18"/>
       <c r="F191" s="18"/>
     </row>
-    <row r="192">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="18"/>
       <c r="B192" s="18"/>
       <c r="C192" s="19"/>
@@ -3746,8 +3738,8 @@
       <c r="E192" s="18"/>
       <c r="F192" s="18"/>
     </row>
-    <row r="193">
-      <c r="A193" s="24" t="s">
+    <row r="193" ht="15.75" customHeight="1">
+      <c r="A193" s="23" t="s">
         <v>78</v>
       </c>
       <c r="B193" s="18"/>
@@ -3756,7 +3748,7 @@
       <c r="E193" s="18"/>
       <c r="F193" s="18"/>
     </row>
-    <row r="194">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="18"/>
       <c r="B194" s="18" t="s">
         <v>11</v>
@@ -3768,7 +3760,7 @@
       <c r="E194" s="18"/>
       <c r="F194" s="18"/>
     </row>
-    <row r="195">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="18"/>
       <c r="B195" s="18" t="s">
         <v>13</v>
@@ -3780,7 +3772,7 @@
       <c r="E195" s="18"/>
       <c r="F195" s="18"/>
     </row>
-    <row r="196">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="18"/>
       <c r="B196" s="18" t="s">
         <v>2</v>
@@ -3792,7 +3784,7 @@
       <c r="E196" s="18"/>
       <c r="F196" s="18"/>
     </row>
-    <row r="197">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="18"/>
       <c r="B197" s="18" t="s">
         <v>14</v>
@@ -3802,19 +3794,19 @@
       <c r="E197" s="18"/>
       <c r="F197" s="18"/>
     </row>
-    <row r="198">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="18"/>
       <c r="B198" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C198" s="25" t="s">
+      <c r="C198" s="24" t="s">
         <v>79</v>
       </c>
       <c r="D198" s="18"/>
       <c r="E198" s="18"/>
       <c r="F198" s="18"/>
     </row>
-    <row r="199">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="18"/>
       <c r="B199" s="18" t="s">
         <v>36</v>
@@ -3826,19 +3818,19 @@
       <c r="E199" s="18"/>
       <c r="F199" s="18"/>
     </row>
-    <row r="200">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="18"/>
-      <c r="B200" s="22" t="s">
+      <c r="B200" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C200" s="23" t="s">
+      <c r="C200" s="22" t="s">
         <v>53</v>
       </c>
       <c r="D200" s="18"/>
       <c r="E200" s="18"/>
       <c r="F200" s="18"/>
     </row>
-    <row r="201">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="18"/>
       <c r="B201" s="18"/>
       <c r="C201" s="19"/>
@@ -3846,8 +3838,8 @@
       <c r="E201" s="18"/>
       <c r="F201" s="18"/>
     </row>
-    <row r="202">
-      <c r="A202" s="24" t="s">
+    <row r="202" ht="15.75" customHeight="1">
+      <c r="A202" s="23" t="s">
         <v>80</v>
       </c>
       <c r="B202" s="18"/>
@@ -3856,7 +3848,7 @@
       <c r="E202" s="18"/>
       <c r="F202" s="18"/>
     </row>
-    <row r="203">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="18"/>
       <c r="B203" s="18" t="s">
         <v>11</v>
@@ -3868,7 +3860,7 @@
       <c r="E203" s="18"/>
       <c r="F203" s="18"/>
     </row>
-    <row r="204">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="18"/>
       <c r="B204" s="18" t="s">
         <v>13</v>
@@ -3880,7 +3872,7 @@
       <c r="E204" s="18"/>
       <c r="F204" s="18"/>
     </row>
-    <row r="205">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="18"/>
       <c r="B205" s="18" t="s">
         <v>2</v>
@@ -3892,7 +3884,7 @@
       <c r="E205" s="18"/>
       <c r="F205" s="18"/>
     </row>
-    <row r="206">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="18"/>
       <c r="B206" s="18" t="s">
         <v>14</v>
@@ -3902,19 +3894,19 @@
       <c r="E206" s="18"/>
       <c r="F206" s="18"/>
     </row>
-    <row r="207">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="18"/>
       <c r="B207" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C207" s="25" t="s">
+      <c r="C207" s="24" t="s">
         <v>81</v>
       </c>
       <c r="D207" s="18"/>
       <c r="E207" s="18"/>
       <c r="F207" s="18"/>
     </row>
-    <row r="208">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="18"/>
       <c r="B208" s="18" t="s">
         <v>36</v>
@@ -3926,19 +3918,19 @@
       <c r="E208" s="18"/>
       <c r="F208" s="18"/>
     </row>
-    <row r="209">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="18"/>
-      <c r="B209" s="22" t="s">
+      <c r="B209" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C209" s="23" t="s">
+      <c r="C209" s="22" t="s">
         <v>83</v>
       </c>
       <c r="D209" s="18"/>
       <c r="E209" s="18"/>
       <c r="F209" s="18"/>
     </row>
-    <row r="210">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="18"/>
       <c r="B210" s="18"/>
       <c r="C210" s="19"/>
@@ -3946,8 +3938,8 @@
       <c r="E210" s="18"/>
       <c r="F210" s="18"/>
     </row>
-    <row r="211">
-      <c r="A211" s="24" t="s">
+    <row r="211" ht="15.75" customHeight="1">
+      <c r="A211" s="23" t="s">
         <v>84</v>
       </c>
       <c r="B211" s="18"/>
@@ -3956,7 +3948,7 @@
       <c r="E211" s="18"/>
       <c r="F211" s="18"/>
     </row>
-    <row r="212">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="18"/>
       <c r="B212" s="18" t="s">
         <v>11</v>
@@ -3968,7 +3960,7 @@
       <c r="E212" s="18"/>
       <c r="F212" s="18"/>
     </row>
-    <row r="213">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="18"/>
       <c r="B213" s="18" t="s">
         <v>13</v>
@@ -3980,7 +3972,7 @@
       <c r="E213" s="18"/>
       <c r="F213" s="18"/>
     </row>
-    <row r="214">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="18"/>
       <c r="B214" s="18" t="s">
         <v>2</v>
@@ -3992,7 +3984,7 @@
       <c r="E214" s="18"/>
       <c r="F214" s="18"/>
     </row>
-    <row r="215">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="18"/>
       <c r="B215" s="18" t="s">
         <v>14</v>
@@ -4002,19 +3994,19 @@
       <c r="E215" s="18"/>
       <c r="F215" s="18"/>
     </row>
-    <row r="216">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="18"/>
       <c r="B216" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C216" s="25" t="s">
+      <c r="C216" s="24" t="s">
         <v>85</v>
       </c>
       <c r="D216" s="18"/>
       <c r="E216" s="18"/>
       <c r="F216" s="18"/>
     </row>
-    <row r="217">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="18"/>
       <c r="B217" s="18" t="s">
         <v>36</v>
@@ -4026,12 +4018,12 @@
       <c r="E217" s="18"/>
       <c r="F217" s="18"/>
     </row>
-    <row r="218">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="18"/>
-      <c r="B218" s="22" t="s">
+      <c r="B218" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C218" s="23" t="s">
+      <c r="C218" s="22" t="s">
         <v>83</v>
       </c>
       <c r="D218" s="18"/>
